--- a/src/beastmistress/assets/data/cutscenes.xlsx
+++ b/src/beastmistress/assets/data/cutscenes.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="debugNPC1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621" refMode="R1C1"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="20">
   <si>
     <t>Type</t>
   </si>
@@ -56,6 +56,24 @@
   </si>
   <si>
     <t>white</t>
+  </si>
+  <si>
+    <t>StartCombat</t>
+  </si>
+  <si>
+    <t>CombatOpponents</t>
+  </si>
+  <si>
+    <t>CombatAllies</t>
+  </si>
+  <si>
+    <t>DebugNPC1</t>
+  </si>
+  <si>
+    <t>CombatBackground</t>
+  </si>
+  <si>
+    <t>maidendeerForest1</t>
   </si>
 </sst>
 </file>
@@ -397,18 +415,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="84.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,8 +451,17 @@
       <c r="G1" t="s">
         <v>12</v>
       </c>
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -453,8 +483,17 @@
       <c r="G2" t="s">
         <v>13</v>
       </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -476,8 +515,17 @@
       <c r="G3" t="s">
         <v>13</v>
       </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -487,16 +535,57 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" t="s">
         <v>7</v>
       </c>
     </row>
